--- a/data/raw/GLNPO 2024 Spring/Ontario/D100/ON 60 QA D100 Spring 2024 24GO00Q53 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Ontario/D100/ON 60 QA D100 Spring 2024 24GO00Q53 Zoop.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\GLNPO 2024 Spring\Ontario\D100\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Ontario\D100\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0240A496-B534-4014-B1F0-740D309F40BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6307E423-6CA7-4ECB-96A7-F3131AC8126E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3797E256-CC4B-4E3E-BD78-76A0C66C6B42}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3797E256-CC4B-4E3E-BD78-76A0C66C6B42}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="6" r:id="rId2"/>
+    <pivotCache cacheId="13" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -3949,7 +3949,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FAD35086-4977-42DF-8782-4E3051AFB834}" name="PivotTable2" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FAD35086-4977-42DF-8782-4E3051AFB834}" name="PivotTable2" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="T2:Y15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="17">
     <pivotField showAll="0"/>
@@ -4386,20 +4386,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB8AA08D-DE49-4338-A2A0-104A698CCB3C}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:Y185"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.88671875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="6" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="3" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="2.44140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4452,7 +4453,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>66</v>
       </c>
@@ -4511,7 +4512,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>66</v>
       </c>
@@ -4582,7 +4583,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>66</v>
       </c>
@@ -4650,7 +4651,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>66</v>
       </c>
@@ -4715,7 +4716,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>66</v>
       </c>
@@ -4783,7 +4784,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>66</v>
       </c>
@@ -4848,7 +4849,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>66</v>
       </c>
@@ -4916,7 +4917,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>66</v>
       </c>
@@ -4984,7 +4985,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>66</v>
       </c>
@@ -5052,7 +5053,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>66</v>
       </c>
@@ -5120,7 +5121,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>66</v>
       </c>
@@ -5188,7 +5189,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>66</v>
       </c>
@@ -5259,7 +5260,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>66</v>
       </c>
@@ -5327,7 +5328,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>66</v>
       </c>
@@ -5398,7 +5399,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>66</v>
       </c>
@@ -5451,7 +5452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>66</v>
       </c>
@@ -5513,7 +5514,7 @@
         <v>0.998</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>66</v>
       </c>
@@ -5573,7 +5574,7 @@
         <v>0.997</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>66</v>
       </c>
@@ -5635,7 +5636,7 @@
         <v>1.0049999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>66</v>
       </c>
@@ -5695,7 +5696,7 @@
         <v>0.996</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>66</v>
       </c>
@@ -5755,7 +5756,7 @@
       </c>
       <c r="V21" s="7"/>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>66</v>
       </c>
@@ -5815,7 +5816,7 @@
       </c>
       <c r="V22" s="7"/>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>66</v>
       </c>
@@ -5872,7 +5873,7 @@
       </c>
       <c r="U23" s="7"/>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>66</v>
       </c>
@@ -5925,7 +5926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>66</v>
       </c>
@@ -5978,7 +5979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>66</v>
       </c>
@@ -6031,7 +6032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>66</v>
       </c>
@@ -6084,7 +6085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>66</v>
       </c>
@@ -6137,7 +6138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>66</v>
       </c>
@@ -6190,7 +6191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>66</v>
       </c>
@@ -6243,7 +6244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -6296,7 +6297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -6349,7 +6350,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>66</v>
       </c>
@@ -6402,7 +6403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>66</v>
       </c>
@@ -6455,7 +6456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>66</v>
       </c>
@@ -6508,7 +6509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>66</v>
       </c>
@@ -6561,7 +6562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>66</v>
       </c>
@@ -6614,7 +6615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>66</v>
       </c>
@@ -6667,7 +6668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>66</v>
       </c>
@@ -6720,7 +6721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>66</v>
       </c>
@@ -6773,7 +6774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>66</v>
       </c>
@@ -6826,7 +6827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>66</v>
       </c>
@@ -6879,7 +6880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>66</v>
       </c>
@@ -6932,7 +6933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>66</v>
       </c>
@@ -6985,7 +6986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>66</v>
       </c>
@@ -7038,7 +7039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>66</v>
       </c>
@@ -7091,7 +7092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>66</v>
       </c>
@@ -7144,7 +7145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>66</v>
       </c>
@@ -7197,7 +7198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>66</v>
       </c>
@@ -7250,7 +7251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>66</v>
       </c>
@@ -7303,7 +7304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>66</v>
       </c>
@@ -7356,7 +7357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>66</v>
       </c>
@@ -7409,7 +7410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>66</v>
       </c>
@@ -7462,7 +7463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>66</v>
       </c>
@@ -7515,7 +7516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>66</v>
       </c>
@@ -7568,7 +7569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>66</v>
       </c>
@@ -7621,7 +7622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>66</v>
       </c>
@@ -7674,7 +7675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>66</v>
       </c>
@@ -7727,7 +7728,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>66</v>
       </c>
@@ -7780,7 +7781,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>66</v>
       </c>
@@ -7833,7 +7834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>66</v>
       </c>
@@ -7886,7 +7887,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>66</v>
       </c>
@@ -7939,7 +7940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>66</v>
       </c>
@@ -7992,7 +7993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>66</v>
       </c>
@@ -8045,7 +8046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>66</v>
       </c>
@@ -8098,7 +8099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>66</v>
       </c>
@@ -8151,7 +8152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>66</v>
       </c>
@@ -8204,7 +8205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>66</v>
       </c>
@@ -8257,7 +8258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>66</v>
       </c>
@@ -8310,7 +8311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>66</v>
       </c>
@@ -8363,7 +8364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>66</v>
       </c>
@@ -8416,7 +8417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>66</v>
       </c>
@@ -8469,7 +8470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>66</v>
       </c>
@@ -8522,7 +8523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>66</v>
       </c>
@@ -8575,7 +8576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>66</v>
       </c>
@@ -8628,7 +8629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>66</v>
       </c>
@@ -8681,7 +8682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>66</v>
       </c>
@@ -8734,7 +8735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>66</v>
       </c>
@@ -8787,7 +8788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>66</v>
       </c>
@@ -8840,7 +8841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>66</v>
       </c>
@@ -8893,7 +8894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>66</v>
       </c>
@@ -8946,7 +8947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>66</v>
       </c>
@@ -8999,7 +9000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>66</v>
       </c>
@@ -9052,7 +9053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>66</v>
       </c>
@@ -9105,7 +9106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>66</v>
       </c>
@@ -9158,7 +9159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>66</v>
       </c>
@@ -9211,7 +9212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>66</v>
       </c>
@@ -9264,7 +9265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>66</v>
       </c>
@@ -9317,7 +9318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>66</v>
       </c>
@@ -9370,7 +9371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>66</v>
       </c>
@@ -9423,7 +9424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>66</v>
       </c>
@@ -9476,7 +9477,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>66</v>
       </c>
@@ -9529,7 +9530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>66</v>
       </c>
@@ -9582,7 +9583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>66</v>
       </c>
@@ -9635,7 +9636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>66</v>
       </c>
@@ -9688,7 +9689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>66</v>
       </c>
@@ -9741,7 +9742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>66</v>
       </c>
@@ -9794,7 +9795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>66</v>
       </c>
@@ -9847,7 +9848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>66</v>
       </c>
@@ -9900,7 +9901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>66</v>
       </c>
@@ -9953,7 +9954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>66</v>
       </c>
@@ -10006,7 +10007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>66</v>
       </c>
@@ -10059,7 +10060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>66</v>
       </c>
@@ -10112,7 +10113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>66</v>
       </c>
@@ -10165,7 +10166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>66</v>
       </c>
@@ -10218,7 +10219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>66</v>
       </c>
@@ -10271,7 +10272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>66</v>
       </c>
@@ -10324,7 +10325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>66</v>
       </c>
@@ -10377,7 +10378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>66</v>
       </c>
@@ -10430,7 +10431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>66</v>
       </c>
@@ -10483,7 +10484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>66</v>
       </c>
@@ -10536,7 +10537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>66</v>
       </c>
@@ -10589,7 +10590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>66</v>
       </c>
@@ -10642,7 +10643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>66</v>
       </c>
@@ -10695,7 +10696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>66</v>
       </c>
@@ -10748,7 +10749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>66</v>
       </c>
@@ -10795,13 +10796,13 @@
         <v>1.0529999999999999</v>
       </c>
       <c r="P116" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="Q116">
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>66</v>
       </c>
@@ -10854,7 +10855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>66</v>
       </c>
@@ -10907,7 +10908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>66</v>
       </c>
@@ -10960,7 +10961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>66</v>
       </c>
@@ -11013,7 +11014,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>66</v>
       </c>
@@ -11066,7 +11067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>66</v>
       </c>
@@ -11119,7 +11120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>66</v>
       </c>
@@ -11172,7 +11173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>66</v>
       </c>
@@ -11225,7 +11226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>66</v>
       </c>
@@ -11278,7 +11279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>66</v>
       </c>
@@ -11331,7 +11332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>66</v>
       </c>
@@ -11384,7 +11385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>66</v>
       </c>
@@ -11437,7 +11438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>66</v>
       </c>
@@ -11490,7 +11491,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>66</v>
       </c>
@@ -11543,7 +11544,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>66</v>
       </c>
@@ -11596,7 +11597,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>66</v>
       </c>
@@ -11649,7 +11650,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>66</v>
       </c>
@@ -11702,7 +11703,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>66</v>
       </c>
@@ -11755,7 +11756,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>66</v>
       </c>
@@ -11808,7 +11809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>66</v>
       </c>
@@ -11861,7 +11862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>66</v>
       </c>
@@ -11914,7 +11915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>66</v>
       </c>
@@ -11967,7 +11968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>66</v>
       </c>
@@ -12020,7 +12021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>66</v>
       </c>
@@ -12073,7 +12074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>66</v>
       </c>
@@ -12126,7 +12127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>66</v>
       </c>
@@ -12179,7 +12180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>66</v>
       </c>
@@ -12232,7 +12233,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>66</v>
       </c>
@@ -12285,7 +12286,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>66</v>
       </c>
@@ -12338,7 +12339,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>66</v>
       </c>
@@ -12391,7 +12392,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>66</v>
       </c>
@@ -12444,7 +12445,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>66</v>
       </c>
@@ -12497,7 +12498,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>66</v>
       </c>
@@ -12550,7 +12551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>66</v>
       </c>
@@ -12603,7 +12604,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>66</v>
       </c>
@@ -12656,7 +12657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>66</v>
       </c>
@@ -12709,7 +12710,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>66</v>
       </c>
@@ -12762,7 +12763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>66</v>
       </c>
@@ -12815,7 +12816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>66</v>
       </c>
@@ -12868,7 +12869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>66</v>
       </c>
@@ -12921,7 +12922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>66</v>
       </c>
@@ -12974,7 +12975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>66</v>
       </c>
@@ -13027,7 +13028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>66</v>
       </c>
@@ -13080,7 +13081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>66</v>
       </c>
@@ -13133,7 +13134,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>66</v>
       </c>
@@ -13186,7 +13187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>66</v>
       </c>
@@ -13239,7 +13240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>66</v>
       </c>
@@ -13292,7 +13293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>66</v>
       </c>
@@ -13345,7 +13346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>66</v>
       </c>
@@ -13401,7 +13402,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="166" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>66</v>
       </c>
@@ -13454,7 +13455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>66</v>
       </c>
@@ -13507,7 +13508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>66</v>
       </c>
@@ -13560,7 +13561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>66</v>
       </c>
@@ -13613,7 +13614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>66</v>
       </c>
@@ -13666,7 +13667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>66</v>
       </c>
@@ -13719,7 +13720,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="172" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>66</v>
       </c>
@@ -13772,7 +13773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>66</v>
       </c>
@@ -13825,7 +13826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>66</v>
       </c>
@@ -13878,7 +13879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>66</v>
       </c>
@@ -13931,7 +13932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>66</v>
       </c>
@@ -13984,7 +13985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>66</v>
       </c>
@@ -14037,7 +14038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>66</v>
       </c>
@@ -14090,7 +14091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>66</v>
       </c>
@@ -14143,7 +14144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="5" t="s">
         <v>66</v>
       </c>
@@ -14197,7 +14198,7 @@
       </c>
       <c r="R180" s="5"/>
     </row>
-    <row r="181" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="5" t="s">
         <v>66</v>
       </c>
@@ -14251,7 +14252,7 @@
       </c>
       <c r="R181" s="5"/>
     </row>
-    <row r="182" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="5" t="s">
         <v>66</v>
       </c>
@@ -14305,7 +14306,7 @@
       </c>
       <c r="R182" s="5"/>
     </row>
-    <row r="183" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="5" t="s">
         <v>66</v>
       </c>
@@ -14358,7 +14359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="5" t="s">
         <v>66</v>
       </c>
@@ -14411,7 +14412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="5" t="s">
         <v>66</v>
       </c>
@@ -14466,9 +14467,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:R185" xr:uid="{EB8AA08D-DE49-4338-A2A0-104A698CCB3C}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A16:R176">
-      <sortCondition ref="L1:L185"/>
-    </sortState>
+    <filterColumn colId="10">
+      <filters>
+        <filter val="Skistodiaptomus oregonensis"/>
+      </filters>
+    </filterColumn>
   </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/raw/GLNPO 2024 Spring/Ontario/D100/ON 60 QA D100 Spring 2024 24GO00Q53 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Ontario/D100/ON 60 QA D100 Spring 2024 24GO00Q53 Zoop.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Ontario\D100\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\GLNPO 2024 Spring\Ontario\D100\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6307E423-6CA7-4ECB-96A7-F3131AC8126E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0240A496-B534-4014-B1F0-740D309F40BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3797E256-CC4B-4E3E-BD78-76A0C66C6B42}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3797E256-CC4B-4E3E-BD78-76A0C66C6B42}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="13" r:id="rId2"/>
+    <pivotCache cacheId="6" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -3949,7 +3949,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FAD35086-4977-42DF-8782-4E3051AFB834}" name="PivotTable2" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FAD35086-4977-42DF-8782-4E3051AFB834}" name="PivotTable2" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="T2:Y15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="17">
     <pivotField showAll="0"/>
@@ -4386,21 +4386,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB8AA08D-DE49-4338-A2A0-104A698CCB3C}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:Y185"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="6" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="3" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="2.44140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="2.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4453,7 +4452,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>66</v>
       </c>
@@ -4512,7 +4511,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>66</v>
       </c>
@@ -4583,7 +4582,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>66</v>
       </c>
@@ -4651,7 +4650,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>66</v>
       </c>
@@ -4716,7 +4715,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>66</v>
       </c>
@@ -4784,7 +4783,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>66</v>
       </c>
@@ -4849,7 +4848,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>66</v>
       </c>
@@ -4917,7 +4916,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>66</v>
       </c>
@@ -4985,7 +4984,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>66</v>
       </c>
@@ -5053,7 +5052,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>66</v>
       </c>
@@ -5121,7 +5120,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>66</v>
       </c>
@@ -5189,7 +5188,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>66</v>
       </c>
@@ -5260,7 +5259,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>66</v>
       </c>
@@ -5328,7 +5327,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>66</v>
       </c>
@@ -5399,7 +5398,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="16" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>66</v>
       </c>
@@ -5452,7 +5451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>66</v>
       </c>
@@ -5514,7 +5513,7 @@
         <v>0.998</v>
       </c>
     </row>
-    <row r="18" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>66</v>
       </c>
@@ -5574,7 +5573,7 @@
         <v>0.997</v>
       </c>
     </row>
-    <row r="19" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>66</v>
       </c>
@@ -5636,7 +5635,7 @@
         <v>1.0049999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>66</v>
       </c>
@@ -5696,7 +5695,7 @@
         <v>0.996</v>
       </c>
     </row>
-    <row r="21" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>66</v>
       </c>
@@ -5756,7 +5755,7 @@
       </c>
       <c r="V21" s="7"/>
     </row>
-    <row r="22" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>66</v>
       </c>
@@ -5816,7 +5815,7 @@
       </c>
       <c r="V22" s="7"/>
     </row>
-    <row r="23" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>66</v>
       </c>
@@ -5873,7 +5872,7 @@
       </c>
       <c r="U23" s="7"/>
     </row>
-    <row r="24" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>66</v>
       </c>
@@ -5926,7 +5925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>66</v>
       </c>
@@ -5979,7 +5978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>66</v>
       </c>
@@ -6032,7 +6031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>66</v>
       </c>
@@ -6085,7 +6084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>66</v>
       </c>
@@ -6138,7 +6137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>66</v>
       </c>
@@ -6191,7 +6190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>66</v>
       </c>
@@ -6244,7 +6243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -6297,7 +6296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -6350,7 +6349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>66</v>
       </c>
@@ -6403,7 +6402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>66</v>
       </c>
@@ -6456,7 +6455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>66</v>
       </c>
@@ -6509,7 +6508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>66</v>
       </c>
@@ -6562,7 +6561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>66</v>
       </c>
@@ -6615,7 +6614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>66</v>
       </c>
@@ -6668,7 +6667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>66</v>
       </c>
@@ -6721,7 +6720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>66</v>
       </c>
@@ -6774,7 +6773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>66</v>
       </c>
@@ -6827,7 +6826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>66</v>
       </c>
@@ -6880,7 +6879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>66</v>
       </c>
@@ -6933,7 +6932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>66</v>
       </c>
@@ -6986,7 +6985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>66</v>
       </c>
@@ -7039,7 +7038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>66</v>
       </c>
@@ -7092,7 +7091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>66</v>
       </c>
@@ -7145,7 +7144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>66</v>
       </c>
@@ -7198,7 +7197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>66</v>
       </c>
@@ -7251,7 +7250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>66</v>
       </c>
@@ -7304,7 +7303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>66</v>
       </c>
@@ -7357,7 +7356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>66</v>
       </c>
@@ -7410,7 +7409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>66</v>
       </c>
@@ -7463,7 +7462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>66</v>
       </c>
@@ -7516,7 +7515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>66</v>
       </c>
@@ -7569,7 +7568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>66</v>
       </c>
@@ -7622,7 +7621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>66</v>
       </c>
@@ -7675,7 +7674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>66</v>
       </c>
@@ -7728,7 +7727,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>66</v>
       </c>
@@ -7781,7 +7780,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>66</v>
       </c>
@@ -7834,7 +7833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>66</v>
       </c>
@@ -7887,7 +7886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>66</v>
       </c>
@@ -7940,7 +7939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>66</v>
       </c>
@@ -7993,7 +7992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>66</v>
       </c>
@@ -8046,7 +8045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>66</v>
       </c>
@@ -8099,7 +8098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>66</v>
       </c>
@@ -8152,7 +8151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>66</v>
       </c>
@@ -8205,7 +8204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>66</v>
       </c>
@@ -8258,7 +8257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>66</v>
       </c>
@@ -8311,7 +8310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>66</v>
       </c>
@@ -8364,7 +8363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>66</v>
       </c>
@@ -8417,7 +8416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>66</v>
       </c>
@@ -8470,7 +8469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>66</v>
       </c>
@@ -8523,7 +8522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>66</v>
       </c>
@@ -8576,7 +8575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>66</v>
       </c>
@@ -8629,7 +8628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>66</v>
       </c>
@@ -8682,7 +8681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>66</v>
       </c>
@@ -8735,7 +8734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>66</v>
       </c>
@@ -8788,7 +8787,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>66</v>
       </c>
@@ -8841,7 +8840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>66</v>
       </c>
@@ -8894,7 +8893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>66</v>
       </c>
@@ -8947,7 +8946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>66</v>
       </c>
@@ -9000,7 +8999,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>66</v>
       </c>
@@ -9053,7 +9052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>66</v>
       </c>
@@ -9106,7 +9105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>66</v>
       </c>
@@ -9159,7 +9158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>66</v>
       </c>
@@ -9212,7 +9211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>66</v>
       </c>
@@ -9265,7 +9264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>66</v>
       </c>
@@ -9318,7 +9317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>66</v>
       </c>
@@ -9371,7 +9370,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>66</v>
       </c>
@@ -9424,7 +9423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>66</v>
       </c>
@@ -9477,7 +9476,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="92" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>66</v>
       </c>
@@ -9530,7 +9529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>66</v>
       </c>
@@ -9583,7 +9582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>66</v>
       </c>
@@ -9636,7 +9635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>66</v>
       </c>
@@ -9689,7 +9688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>66</v>
       </c>
@@ -9742,7 +9741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>66</v>
       </c>
@@ -9795,7 +9794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>66</v>
       </c>
@@ -9848,7 +9847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>66</v>
       </c>
@@ -9901,7 +9900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>66</v>
       </c>
@@ -9954,7 +9953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>66</v>
       </c>
@@ -10007,7 +10006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>66</v>
       </c>
@@ -10060,7 +10059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>66</v>
       </c>
@@ -10113,7 +10112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>66</v>
       </c>
@@ -10166,7 +10165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>66</v>
       </c>
@@ -10219,7 +10218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>66</v>
       </c>
@@ -10272,7 +10271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>66</v>
       </c>
@@ -10325,7 +10324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>66</v>
       </c>
@@ -10378,7 +10377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>66</v>
       </c>
@@ -10431,7 +10430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>66</v>
       </c>
@@ -10484,7 +10483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>66</v>
       </c>
@@ -10537,7 +10536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>66</v>
       </c>
@@ -10590,7 +10589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>66</v>
       </c>
@@ -10643,7 +10642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>66</v>
       </c>
@@ -10696,7 +10695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>66</v>
       </c>
@@ -10749,7 +10748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>66</v>
       </c>
@@ -10796,13 +10795,13 @@
         <v>1.0529999999999999</v>
       </c>
       <c r="P116" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="Q116">
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>66</v>
       </c>
@@ -10855,7 +10854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>66</v>
       </c>
@@ -10908,7 +10907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>66</v>
       </c>
@@ -10961,7 +10960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>66</v>
       </c>
@@ -11014,7 +11013,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="121" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>66</v>
       </c>
@@ -11067,7 +11066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>66</v>
       </c>
@@ -11120,7 +11119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>66</v>
       </c>
@@ -11173,7 +11172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>66</v>
       </c>
@@ -11226,7 +11225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>66</v>
       </c>
@@ -11279,7 +11278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>66</v>
       </c>
@@ -11332,7 +11331,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>66</v>
       </c>
@@ -11385,7 +11384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>66</v>
       </c>
@@ -11438,7 +11437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>66</v>
       </c>
@@ -11491,7 +11490,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="130" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>66</v>
       </c>
@@ -11544,7 +11543,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="131" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>66</v>
       </c>
@@ -11597,7 +11596,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="132" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>66</v>
       </c>
@@ -11650,7 +11649,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="133" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>66</v>
       </c>
@@ -11703,7 +11702,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>66</v>
       </c>
@@ -11756,7 +11755,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="135" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>66</v>
       </c>
@@ -11809,7 +11808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>66</v>
       </c>
@@ -11862,7 +11861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>66</v>
       </c>
@@ -11915,7 +11914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>66</v>
       </c>
@@ -11968,7 +11967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>66</v>
       </c>
@@ -12021,7 +12020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>66</v>
       </c>
@@ -12074,7 +12073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>66</v>
       </c>
@@ -12127,7 +12126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>66</v>
       </c>
@@ -12180,7 +12179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>66</v>
       </c>
@@ -12233,7 +12232,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="144" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>66</v>
       </c>
@@ -12286,7 +12285,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="145" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>66</v>
       </c>
@@ -12339,7 +12338,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="146" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>66</v>
       </c>
@@ -12392,7 +12391,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="147" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>66</v>
       </c>
@@ -12445,7 +12444,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="148" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>66</v>
       </c>
@@ -12498,7 +12497,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="149" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>66</v>
       </c>
@@ -12551,7 +12550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>66</v>
       </c>
@@ -12604,7 +12603,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="151" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>66</v>
       </c>
@@ -12657,7 +12656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>66</v>
       </c>
@@ -12710,7 +12709,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>66</v>
       </c>
@@ -12763,7 +12762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>66</v>
       </c>
@@ -12816,7 +12815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>66</v>
       </c>
@@ -12869,7 +12868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>66</v>
       </c>
@@ -12922,7 +12921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>66</v>
       </c>
@@ -12975,7 +12974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>66</v>
       </c>
@@ -13028,7 +13027,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>66</v>
       </c>
@@ -13081,7 +13080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>66</v>
       </c>
@@ -13134,7 +13133,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>66</v>
       </c>
@@ -13187,7 +13186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>66</v>
       </c>
@@ -13240,7 +13239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>66</v>
       </c>
@@ -13293,7 +13292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>66</v>
       </c>
@@ -13346,7 +13345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>66</v>
       </c>
@@ -13402,7 +13401,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="166" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>66</v>
       </c>
@@ -13455,7 +13454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>66</v>
       </c>
@@ -13508,7 +13507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>66</v>
       </c>
@@ -13561,7 +13560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>66</v>
       </c>
@@ -13614,7 +13613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>66</v>
       </c>
@@ -13667,7 +13666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>66</v>
       </c>
@@ -13720,7 +13719,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="172" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>66</v>
       </c>
@@ -13773,7 +13772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>66</v>
       </c>
@@ -13826,7 +13825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>66</v>
       </c>
@@ -13879,7 +13878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>66</v>
       </c>
@@ -13932,7 +13931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>66</v>
       </c>
@@ -13985,7 +13984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>66</v>
       </c>
@@ -14038,7 +14037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>66</v>
       </c>
@@ -14091,7 +14090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>66</v>
       </c>
@@ -14144,7 +14143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A180" s="5" t="s">
         <v>66</v>
       </c>
@@ -14198,7 +14197,7 @@
       </c>
       <c r="R180" s="5"/>
     </row>
-    <row r="181" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A181" s="5" t="s">
         <v>66</v>
       </c>
@@ -14252,7 +14251,7 @@
       </c>
       <c r="R181" s="5"/>
     </row>
-    <row r="182" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A182" s="5" t="s">
         <v>66</v>
       </c>
@@ -14306,7 +14305,7 @@
       </c>
       <c r="R182" s="5"/>
     </row>
-    <row r="183" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A183" s="5" t="s">
         <v>66</v>
       </c>
@@ -14359,7 +14358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A184" s="5" t="s">
         <v>66</v>
       </c>
@@ -14412,7 +14411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A185" s="5" t="s">
         <v>66</v>
       </c>
@@ -14467,11 +14466,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:R185" xr:uid="{EB8AA08D-DE49-4338-A2A0-104A698CCB3C}">
-    <filterColumn colId="10">
-      <filters>
-        <filter val="Skistodiaptomus oregonensis"/>
-      </filters>
-    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A16:R176">
+      <sortCondition ref="L1:L185"/>
+    </sortState>
   </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/raw/GLNPO 2024 Spring/Ontario/D100/ON 60 QA D100 Spring 2024 24GO00Q53 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Ontario/D100/ON 60 QA D100 Spring 2024 24GO00Q53 Zoop.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\GLNPO 2024 Spring\Ontario\D100\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Ontario\D100\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0240A496-B534-4014-B1F0-740D309F40BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F118B5C3-CD15-402B-9B4C-C1D76E8AF043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3797E256-CC4B-4E3E-BD78-76A0C66C6B42}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{3797E256-CC4B-4E3E-BD78-76A0C66C6B42}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="6" r:id="rId2"/>
+    <pivotCache cacheId="1" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -3949,7 +3949,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FAD35086-4977-42DF-8782-4E3051AFB834}" name="PivotTable2" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FAD35086-4977-42DF-8782-4E3051AFB834}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="T2:Y15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="17">
     <pivotField showAll="0"/>
@@ -4386,20 +4386,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB8AA08D-DE49-4338-A2A0-104A698CCB3C}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:Y185"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.88671875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="6" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="3" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="2.44140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4452,7 +4454,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>66</v>
       </c>
@@ -4511,7 +4513,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>66</v>
       </c>
@@ -4582,7 +4584,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>66</v>
       </c>
@@ -4650,7 +4652,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>66</v>
       </c>
@@ -4715,7 +4717,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>66</v>
       </c>
@@ -4783,7 +4785,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>66</v>
       </c>
@@ -4848,7 +4850,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>66</v>
       </c>
@@ -4916,7 +4918,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>66</v>
       </c>
@@ -4984,7 +4986,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>66</v>
       </c>
@@ -5052,7 +5054,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>66</v>
       </c>
@@ -5120,7 +5122,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>66</v>
       </c>
@@ -5188,7 +5190,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>66</v>
       </c>
@@ -5259,7 +5261,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>66</v>
       </c>
@@ -5327,7 +5329,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>66</v>
       </c>
@@ -5398,7 +5400,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>66</v>
       </c>
@@ -5451,7 +5453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>66</v>
       </c>
@@ -5513,7 +5515,7 @@
         <v>0.998</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>66</v>
       </c>
@@ -5573,7 +5575,7 @@
         <v>0.997</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>66</v>
       </c>
@@ -5635,7 +5637,7 @@
         <v>1.0049999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>66</v>
       </c>
@@ -5695,7 +5697,7 @@
         <v>0.996</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>66</v>
       </c>
@@ -5755,7 +5757,7 @@
       </c>
       <c r="V21" s="7"/>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>66</v>
       </c>
@@ -5815,7 +5817,7 @@
       </c>
       <c r="V22" s="7"/>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>66</v>
       </c>
@@ -5872,7 +5874,7 @@
       </c>
       <c r="U23" s="7"/>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>66</v>
       </c>
@@ -5925,7 +5927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>66</v>
       </c>
@@ -5978,7 +5980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>66</v>
       </c>
@@ -6031,7 +6033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>66</v>
       </c>
@@ -6084,7 +6086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>66</v>
       </c>
@@ -6137,7 +6139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>66</v>
       </c>
@@ -6190,7 +6192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>66</v>
       </c>
@@ -6243,7 +6245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -6296,7 +6298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -6349,7 +6351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>66</v>
       </c>
@@ -6402,7 +6404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>66</v>
       </c>
@@ -6455,7 +6457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>66</v>
       </c>
@@ -6508,7 +6510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>66</v>
       </c>
@@ -6561,7 +6563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>66</v>
       </c>
@@ -6614,7 +6616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>66</v>
       </c>
@@ -6667,7 +6669,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>66</v>
       </c>
@@ -6720,7 +6722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>66</v>
       </c>
@@ -6773,7 +6775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>66</v>
       </c>
@@ -6826,7 +6828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>66</v>
       </c>
@@ -6879,7 +6881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>66</v>
       </c>
@@ -6932,7 +6934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>66</v>
       </c>
@@ -6985,7 +6987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>66</v>
       </c>
@@ -7038,7 +7040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>66</v>
       </c>
@@ -7091,7 +7093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>66</v>
       </c>
@@ -7144,7 +7146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>66</v>
       </c>
@@ -7197,7 +7199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>66</v>
       </c>
@@ -7250,7 +7252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>66</v>
       </c>
@@ -7303,7 +7305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>66</v>
       </c>
@@ -7356,7 +7358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>66</v>
       </c>
@@ -7409,7 +7411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>66</v>
       </c>
@@ -7462,7 +7464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>66</v>
       </c>
@@ -7515,7 +7517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>66</v>
       </c>
@@ -7568,7 +7570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>66</v>
       </c>
@@ -7621,7 +7623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>66</v>
       </c>
@@ -7674,7 +7676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>66</v>
       </c>
@@ -7727,7 +7729,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>66</v>
       </c>
@@ -7780,7 +7782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>66</v>
       </c>
@@ -7833,7 +7835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>66</v>
       </c>
@@ -7886,7 +7888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>66</v>
       </c>
@@ -7939,7 +7941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>66</v>
       </c>
@@ -7992,7 +7994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>66</v>
       </c>
@@ -8045,7 +8047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>66</v>
       </c>
@@ -8098,7 +8100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>66</v>
       </c>
@@ -8151,7 +8153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>66</v>
       </c>
@@ -8204,7 +8206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>66</v>
       </c>
@@ -8257,7 +8259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>66</v>
       </c>
@@ -8310,7 +8312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>66</v>
       </c>
@@ -8363,7 +8365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>66</v>
       </c>
@@ -8416,7 +8418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>66</v>
       </c>
@@ -8469,7 +8471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>66</v>
       </c>
@@ -8522,7 +8524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>66</v>
       </c>
@@ -8575,7 +8577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>66</v>
       </c>
@@ -8628,7 +8630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>66</v>
       </c>
@@ -8681,7 +8683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>66</v>
       </c>
@@ -8734,7 +8736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>66</v>
       </c>
@@ -8787,7 +8789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>66</v>
       </c>
@@ -8840,7 +8842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>66</v>
       </c>
@@ -8893,7 +8895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>66</v>
       </c>
@@ -8946,7 +8948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>66</v>
       </c>
@@ -8999,7 +9001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>66</v>
       </c>
@@ -9052,7 +9054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>66</v>
       </c>
@@ -9105,7 +9107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>66</v>
       </c>
@@ -9158,7 +9160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>66</v>
       </c>
@@ -9211,7 +9213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>66</v>
       </c>
@@ -9264,7 +9266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>66</v>
       </c>
@@ -9317,7 +9319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>66</v>
       </c>
@@ -9370,7 +9372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>66</v>
       </c>
@@ -9423,7 +9425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>66</v>
       </c>
@@ -9476,7 +9478,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>66</v>
       </c>
@@ -9529,7 +9531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>66</v>
       </c>
@@ -9582,7 +9584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>66</v>
       </c>
@@ -9635,7 +9637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>66</v>
       </c>
@@ -9688,7 +9690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>66</v>
       </c>
@@ -9741,7 +9743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>66</v>
       </c>
@@ -9794,7 +9796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>66</v>
       </c>
@@ -9847,7 +9849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>66</v>
       </c>
@@ -9900,7 +9902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>66</v>
       </c>
@@ -9953,7 +9955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>66</v>
       </c>
@@ -10006,7 +10008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>66</v>
       </c>
@@ -10059,7 +10061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>66</v>
       </c>
@@ -10112,7 +10114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>66</v>
       </c>
@@ -10165,7 +10167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>66</v>
       </c>
@@ -10218,7 +10220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>66</v>
       </c>
@@ -10271,7 +10273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>66</v>
       </c>
@@ -10324,7 +10326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>66</v>
       </c>
@@ -10377,7 +10379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>66</v>
       </c>
@@ -10430,7 +10432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>66</v>
       </c>
@@ -10483,7 +10485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>66</v>
       </c>
@@ -10536,7 +10538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>66</v>
       </c>
@@ -10589,7 +10591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>66</v>
       </c>
@@ -10642,7 +10644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>66</v>
       </c>
@@ -10695,7 +10697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>66</v>
       </c>
@@ -10748,7 +10750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>66</v>
       </c>
@@ -10795,13 +10797,13 @@
         <v>1.0529999999999999</v>
       </c>
       <c r="P116" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="Q116">
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>66</v>
       </c>
@@ -10854,7 +10856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>66</v>
       </c>
@@ -10907,7 +10909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>66</v>
       </c>
@@ -10960,7 +10962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>66</v>
       </c>
@@ -11013,7 +11015,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>66</v>
       </c>
@@ -11066,7 +11068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>66</v>
       </c>
@@ -11119,7 +11121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>66</v>
       </c>
@@ -11172,7 +11174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>66</v>
       </c>
@@ -11225,7 +11227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>66</v>
       </c>
@@ -11278,7 +11280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>66</v>
       </c>
@@ -11331,7 +11333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>66</v>
       </c>
@@ -11384,7 +11386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>66</v>
       </c>
@@ -11437,7 +11439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>66</v>
       </c>
@@ -11490,7 +11492,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>66</v>
       </c>
@@ -11543,7 +11545,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>66</v>
       </c>
@@ -11596,7 +11598,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>66</v>
       </c>
@@ -11649,7 +11651,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>66</v>
       </c>
@@ -11702,7 +11704,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>66</v>
       </c>
@@ -11755,7 +11757,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>66</v>
       </c>
@@ -11808,7 +11810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>66</v>
       </c>
@@ -11861,7 +11863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>66</v>
       </c>
@@ -11914,7 +11916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>66</v>
       </c>
@@ -11967,7 +11969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>66</v>
       </c>
@@ -12020,7 +12022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>66</v>
       </c>
@@ -12073,7 +12075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>66</v>
       </c>
@@ -12126,7 +12128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>66</v>
       </c>
@@ -12179,7 +12181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>66</v>
       </c>
@@ -12232,7 +12234,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>66</v>
       </c>
@@ -12285,7 +12287,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>66</v>
       </c>
@@ -12338,7 +12340,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>66</v>
       </c>
@@ -12391,7 +12393,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>66</v>
       </c>
@@ -12444,7 +12446,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>66</v>
       </c>
@@ -12497,7 +12499,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>66</v>
       </c>
@@ -12550,7 +12552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>66</v>
       </c>
@@ -12603,7 +12605,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>66</v>
       </c>
@@ -12656,7 +12658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>66</v>
       </c>
@@ -12709,7 +12711,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>66</v>
       </c>
@@ -12762,7 +12764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>66</v>
       </c>
@@ -12815,7 +12817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>66</v>
       </c>
@@ -12868,7 +12870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>66</v>
       </c>
@@ -12921,7 +12923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>66</v>
       </c>
@@ -12974,7 +12976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>66</v>
       </c>
@@ -13027,7 +13029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>66</v>
       </c>
@@ -13080,7 +13082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>66</v>
       </c>
@@ -13133,7 +13135,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>66</v>
       </c>
@@ -13186,7 +13188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>66</v>
       </c>
@@ -13239,7 +13241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>66</v>
       </c>
@@ -13292,7 +13294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>66</v>
       </c>
@@ -13345,7 +13347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>66</v>
       </c>
@@ -13401,7 +13403,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="166" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>66</v>
       </c>
@@ -13454,7 +13456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>66</v>
       </c>
@@ -13507,7 +13509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>66</v>
       </c>
@@ -13560,7 +13562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>66</v>
       </c>
@@ -13613,7 +13615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>66</v>
       </c>
@@ -13666,7 +13668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>66</v>
       </c>
@@ -13719,7 +13721,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="172" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>66</v>
       </c>
@@ -13772,7 +13774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>66</v>
       </c>
@@ -13825,7 +13827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>66</v>
       </c>
@@ -13878,7 +13880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>66</v>
       </c>
@@ -13931,7 +13933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>66</v>
       </c>
@@ -13984,7 +13986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>66</v>
       </c>
@@ -14037,7 +14039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>66</v>
       </c>
@@ -14090,7 +14092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>66</v>
       </c>
@@ -14143,7 +14145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="5" t="s">
         <v>66</v>
       </c>
@@ -14197,7 +14199,7 @@
       </c>
       <c r="R180" s="5"/>
     </row>
-    <row r="181" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="5" t="s">
         <v>66</v>
       </c>
@@ -14251,7 +14253,7 @@
       </c>
       <c r="R181" s="5"/>
     </row>
-    <row r="182" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="5" t="s">
         <v>66</v>
       </c>
@@ -14305,7 +14307,7 @@
       </c>
       <c r="R182" s="5"/>
     </row>
-    <row r="183" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="5" t="s">
         <v>66</v>
       </c>
@@ -14358,7 +14360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="5" t="s">
         <v>66</v>
       </c>
@@ -14411,7 +14413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="5" t="s">
         <v>66</v>
       </c>
@@ -14466,6 +14468,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:R185" xr:uid="{EB8AA08D-DE49-4338-A2A0-104A698CCB3C}">
+    <filterColumn colId="10">
+      <filters>
+        <filter val="Skistodiaptomus oregonensis"/>
+      </filters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A16:R176">
       <sortCondition ref="L1:L185"/>
     </sortState>
